--- a/Lezione 1 - Iris_Lab_Excel.xlsx
+++ b/Lezione 1 - Iris_Lab_Excel.xlsx
@@ -1,35 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onitgroup.sharepoint.com/sites/AreaConsulting-CorsoUniboLabMLOttimizzazione/Documenti condivisi/Corso Unibo Lab ML, Ottimizzazione/Corso 2026 - Onit/Modulo 2/Pratica ed Esercitazioni/Nostra/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmorelli\IdeaProjects\B3099---LABORATORIO-DI-OTTIMIZZAZIONE-INTELLIGENZA-ARTIFICIALE-E-MACHINE-LEARNING---2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="13_ncr:1_{5BE558CB-6808-419C-AB3F-4389E04D401B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8D90907-134F-40CD-A7AB-37D76F9C9049}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CAD2D0-D190-4F57-A666-CFDA9C061E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni" sheetId="1" r:id="rId1"/>
     <sheet name="Dati_grezzi" sheetId="2" r:id="rId2"/>
     <sheet name="Statistiche_guidate" sheetId="3" r:id="rId3"/>
-    <sheet name="Preprocessing" sheetId="4" r:id="rId4"/>
-    <sheet name="Outlier_IQR" sheetId="5" r:id="rId5"/>
-    <sheet name="Scatter" sheetId="6" r:id="rId6"/>
-    <sheet name="Distribuzioni" sheetId="7" r:id="rId7"/>
-    <sheet name="Chi Quadro" sheetId="11" r:id="rId8"/>
-    <sheet name="Consegna" sheetId="8" r:id="rId9"/>
+    <sheet name="Distribuzioni" sheetId="7" r:id="rId4"/>
+    <sheet name="Scatter" sheetId="6" r:id="rId5"/>
+    <sheet name="Preprocessing" sheetId="4" r:id="rId6"/>
+    <sheet name="Outlier_IQR" sheetId="5" r:id="rId7"/>
+    <sheet name="Dettagli1" sheetId="12" r:id="rId8"/>
+    <sheet name="Chi Quadro" sheetId="11" r:id="rId9"/>
+    <sheet name="Consegna" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dati_grezzi!$A$1:$E$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Outlier_IQR!$A$4:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Outlier_IQR!$A$4:$I$4</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="2099" r:id="rId10"/>
+    <pivotCache cacheId="5" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="77">
   <si>
     <t>Laboratorio 1 – Iris (Excel 365, IT)</t>
   </si>
@@ -240,9 +241,6 @@
     <t>Valori attesi, li calcoliamo come:  ((valore riga)*(totale colonna))/(totale complessivo)</t>
   </si>
   <si>
-    <t>Quindi, applichiamo il chi quadro)</t>
-  </si>
-  <si>
     <t>la nostra H0 era che le due sono indipendenti, è vero?</t>
   </si>
   <si>
@@ -266,12 +264,33 @@
   <si>
     <t>Q5) Perché è importante standardizzare prima di alcuni modelli?</t>
   </si>
+  <si>
+    <t>Lunghezza del petalo</t>
+  </si>
+  <si>
+    <t>Setosa</t>
+  </si>
+  <si>
+    <t>Versicolor</t>
+  </si>
+  <si>
+    <t>Virginica</t>
+  </si>
+  <si>
+    <t>Quindi, applichiamo il chi quadro</t>
+  </si>
+  <si>
+    <t>Test T</t>
+  </si>
+  <si>
+    <t>Dettagli per Somma di Contatore - species: virginica, bin: Alto</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +312,20 @@
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -320,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -338,10 +371,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -360,7 +396,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giorgia Morelli" refreshedDate="46076.45814328704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="150" xr:uid="{517BB81A-8A5C-4565-91A9-F12843244D67}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giorgia Morelli" refreshedDate="46080.713944328701" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="150" xr:uid="{517BB81A-8A5C-4565-91A9-F12843244D67}">
   <cacheSource type="worksheet">
     <worksheetSource ref="E1:G151" sheet="Dati_grezzi"/>
   </cacheSource>
@@ -655,7 +691,7 @@
   </r>
   <r>
     <x v="1"/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -755,7 +791,7 @@
   </r>
   <r>
     <x v="1"/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -1000,7 +1036,7 @@
   </r>
   <r>
     <x v="2"/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -1010,7 +1046,7 @@
   </r>
   <r>
     <x v="2"/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -1030,7 +1066,7 @@
   </r>
   <r>
     <x v="2"/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -1147,7 +1183,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30BC0138-36EC-407B-9CFD-362C426E4BE0}" name="Tabella pivot2" cacheId="2099" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30BC0138-36EC-407B-9CFD-362C426E4BE0}" name="Tabella pivot2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -1215,6 +1251,18 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{54BDAE5D-A46C-4D6C-AC97-7707B981486E}" name="Tabella1" displayName="Tabella1" ref="A3:C50" totalsRowShown="0">
+  <autoFilter ref="A3:C50" xr:uid="{54BDAE5D-A46C-4D6C-AC97-7707B981486E}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{833068E0-2309-4183-98A7-7FBCA329A4D3}" name="species"/>
+    <tableColumn id="2" xr3:uid="{8B1BE7E6-6C4E-46F7-966C-58C1023B6EEA}" name="bin"/>
+    <tableColumn id="3" xr3:uid="{AD18D3FE-4A6B-4168-BA91-4CB7D5B4CBC2}" name="Contatore"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1503,54 +1551,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="30">
+    <row r="5" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1561,20 +1657,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O151"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0.7109375" customWidth="1"/>
-    <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="1.85546875" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -1596,11 +1694,14 @@
       <c r="G1" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="O1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5.0999999999999996</v>
       </c>
@@ -1624,15 +1725,15 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <f>TTEST(B2:B51,B52:B101,2,3)</f>
-        <v>2.4842278957475381E-15</v>
+        <f>TTEST(C2:C51,C52:C101,2,3)</f>
+        <v>9.9344329575875926E-46</v>
       </c>
       <c r="O2">
-        <f>_xlfn.PERCENTILE.INC(Dati_grezzi!C2:C151,0.33)</f>
-        <v>2.087000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <f>_xlfn.PERCENTILE.INC(Dati_grezzi!C2:C151,0.3333)</f>
+        <v>2.6278699999999957</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4.9000000000000004</v>
       </c>
@@ -1656,11 +1757,11 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <f>_xlfn.PERCENTILE.INC(Dati_grezzi!C2:C151,0.66)</f>
-        <v>4.8340000000000005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <f>_xlfn.PERCENTILE.INC(Dati_grezzi!C2:C151,0.66666)</f>
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4.7</v>
       </c>
@@ -1684,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4.5999999999999996</v>
       </c>
@@ -1708,7 +1809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1732,7 +1833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5.4</v>
       </c>
@@ -1756,7 +1857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4.5999999999999996</v>
       </c>
@@ -1780,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1804,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>4.4000000000000004</v>
       </c>
@@ -1828,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>4.9000000000000004</v>
       </c>
@@ -1852,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5.4</v>
       </c>
@@ -1876,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4.8</v>
       </c>
@@ -1900,7 +2001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4.8</v>
       </c>
@@ -1924,7 +2025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4.3</v>
       </c>
@@ -1948,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>5.8</v>
       </c>
@@ -1972,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>5.7</v>
       </c>
@@ -1996,7 +2097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5.4</v>
       </c>
@@ -2020,7 +2121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5.0999999999999996</v>
       </c>
@@ -2044,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>5.7</v>
       </c>
@@ -2068,7 +2169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5.0999999999999996</v>
       </c>
@@ -2092,7 +2193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>5.4</v>
       </c>
@@ -2116,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>5.0999999999999996</v>
       </c>
@@ -2140,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4.5999999999999996</v>
       </c>
@@ -2164,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>5.0999999999999996</v>
       </c>
@@ -2188,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4.8</v>
       </c>
@@ -2212,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>5</v>
       </c>
@@ -2236,7 +2337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5</v>
       </c>
@@ -2260,7 +2361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>5.2</v>
       </c>
@@ -2284,7 +2385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5.2</v>
       </c>
@@ -2308,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4.7</v>
       </c>
@@ -2332,7 +2433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>4.8</v>
       </c>
@@ -2356,7 +2457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>5.4</v>
       </c>
@@ -2380,7 +2481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5.2</v>
       </c>
@@ -2404,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5.5</v>
       </c>
@@ -2428,7 +2529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>4.9000000000000004</v>
       </c>
@@ -2452,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
@@ -2476,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>5.5</v>
       </c>
@@ -2500,7 +2601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>4.9000000000000004</v>
       </c>
@@ -2524,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>4.4000000000000004</v>
       </c>
@@ -2548,7 +2649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>5.0999999999999996</v>
       </c>
@@ -2572,7 +2673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5</v>
       </c>
@@ -2596,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>4.5</v>
       </c>
@@ -2620,7 +2721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>4.4000000000000004</v>
       </c>
@@ -2644,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>5</v>
       </c>
@@ -2668,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>5.0999999999999996</v>
       </c>
@@ -2692,7 +2793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4.8</v>
       </c>
@@ -2716,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5.0999999999999996</v>
       </c>
@@ -2740,7 +2841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>4.5999999999999996</v>
       </c>
@@ -2764,7 +2865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>5.3</v>
       </c>
@@ -2788,7 +2889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2812,7 +2913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>7</v>
       </c>
@@ -2836,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>6.4</v>
       </c>
@@ -2860,7 +2961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>6.9</v>
       </c>
@@ -2878,13 +2979,13 @@
       </c>
       <c r="F54" t="str">
         <f>IF(Dati_grezzi!C54&lt;=$O$2,"Basso",IF(C54&lt;=$O$3,"Medio","Alto"))</f>
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>5.5</v>
       </c>
@@ -2908,7 +3009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>6.5</v>
       </c>
@@ -2932,7 +3033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>5.7</v>
       </c>
@@ -2956,7 +3057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>6.3</v>
       </c>
@@ -2980,7 +3081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4.9000000000000004</v>
       </c>
@@ -3004,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>6.6</v>
       </c>
@@ -3028,7 +3129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>5.2</v>
       </c>
@@ -3052,7 +3153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>5</v>
       </c>
@@ -3076,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>5.9</v>
       </c>
@@ -3100,7 +3201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>6</v>
       </c>
@@ -3124,7 +3225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>6.1</v>
       </c>
@@ -3148,7 +3249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>5.6</v>
       </c>
@@ -3172,7 +3273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>6.7</v>
       </c>
@@ -3196,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>5.6</v>
       </c>
@@ -3220,7 +3321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>5.8</v>
       </c>
@@ -3244,7 +3345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>6.2</v>
       </c>
@@ -3268,7 +3369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>5.6</v>
       </c>
@@ -3292,7 +3393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>5.9</v>
       </c>
@@ -3316,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>6.1</v>
       </c>
@@ -3340,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>6.3</v>
       </c>
@@ -3358,13 +3459,13 @@
       </c>
       <c r="F74" t="str">
         <f>IF(Dati_grezzi!C74&lt;=$O$2,"Basso",IF(C74&lt;=$O$3,"Medio","Alto"))</f>
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>6.1</v>
       </c>
@@ -3388,7 +3489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>6.4</v>
       </c>
@@ -3412,7 +3513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>6.6</v>
       </c>
@@ -3436,7 +3537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>6.8</v>
       </c>
@@ -3460,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>6.7</v>
       </c>
@@ -3484,7 +3585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>6</v>
       </c>
@@ -3508,7 +3609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>5.7</v>
       </c>
@@ -3532,7 +3633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>5.5</v>
       </c>
@@ -3556,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>5.5</v>
       </c>
@@ -3580,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>5.8</v>
       </c>
@@ -3604,7 +3705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>6</v>
       </c>
@@ -3628,7 +3729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>5.4</v>
       </c>
@@ -3652,7 +3753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>6</v>
       </c>
@@ -3676,7 +3777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>6.7</v>
       </c>
@@ -3700,7 +3801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>6.3</v>
       </c>
@@ -3724,7 +3825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>5.6</v>
       </c>
@@ -3748,7 +3849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>5.5</v>
       </c>
@@ -3772,7 +3873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>5.5</v>
       </c>
@@ -3796,7 +3897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>6.1</v>
       </c>
@@ -3820,7 +3921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>5.8</v>
       </c>
@@ -3844,7 +3945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>5</v>
       </c>
@@ -3868,7 +3969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>5.6</v>
       </c>
@@ -3892,7 +3993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>5.7</v>
       </c>
@@ -3916,7 +4017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>5.7</v>
       </c>
@@ -3940,7 +4041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>6.2</v>
       </c>
@@ -3964,7 +4065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>5.0999999999999996</v>
       </c>
@@ -3988,7 +4089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>5.7</v>
       </c>
@@ -4012,7 +4113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>6.3</v>
       </c>
@@ -4036,7 +4137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>5.8</v>
       </c>
@@ -4060,7 +4161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>7.1</v>
       </c>
@@ -4084,7 +4185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>6.3</v>
       </c>
@@ -4108,7 +4209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>6.5</v>
       </c>
@@ -4132,7 +4233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>7.6</v>
       </c>
@@ -4156,7 +4257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>4.9000000000000004</v>
       </c>
@@ -4180,7 +4281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>7.3</v>
       </c>
@@ -4204,7 +4305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>6.7</v>
       </c>
@@ -4228,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>7.2</v>
       </c>
@@ -4252,7 +4353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>6.5</v>
       </c>
@@ -4276,7 +4377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>6.4</v>
       </c>
@@ -4300,7 +4401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>6.8</v>
       </c>
@@ -4324,7 +4425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>5.7</v>
       </c>
@@ -4348,7 +4449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>5.8</v>
       </c>
@@ -4372,7 +4473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>6.4</v>
       </c>
@@ -4396,7 +4497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>6.5</v>
       </c>
@@ -4420,7 +4521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>7.7</v>
       </c>
@@ -4444,7 +4545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>7.7</v>
       </c>
@@ -4468,7 +4569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>6</v>
       </c>
@@ -4492,7 +4593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>6.9</v>
       </c>
@@ -4516,7 +4617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>5.6</v>
       </c>
@@ -4534,13 +4635,13 @@
       </c>
       <c r="F123" t="str">
         <f>IF(Dati_grezzi!C123&lt;=$O$2,"Basso",IF(C123&lt;=$O$3,"Medio","Alto"))</f>
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G123">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>7.7</v>
       </c>
@@ -4564,7 +4665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>6.3</v>
       </c>
@@ -4582,13 +4683,13 @@
       </c>
       <c r="F125" t="str">
         <f>IF(Dati_grezzi!C125&lt;=$O$2,"Basso",IF(C125&lt;=$O$3,"Medio","Alto"))</f>
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>6.7</v>
       </c>
@@ -4612,7 +4713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>7.2</v>
       </c>
@@ -4636,7 +4737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>6.2</v>
       </c>
@@ -4660,7 +4761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>6.1</v>
       </c>
@@ -4678,13 +4779,13 @@
       </c>
       <c r="F129" t="str">
         <f>IF(Dati_grezzi!C129&lt;=$O$2,"Basso",IF(C129&lt;=$O$3,"Medio","Alto"))</f>
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G129">
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>6.4</v>
       </c>
@@ -4708,7 +4809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>7.2</v>
       </c>
@@ -4732,7 +4833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>7.4</v>
       </c>
@@ -4756,7 +4857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>7.9</v>
       </c>
@@ -4780,7 +4881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>6.4</v>
       </c>
@@ -4804,7 +4905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>6.3</v>
       </c>
@@ -4828,7 +4929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>6.1</v>
       </c>
@@ -4852,7 +4953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>7.7</v>
       </c>
@@ -4876,7 +4977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>6.3</v>
       </c>
@@ -4900,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>6.4</v>
       </c>
@@ -4924,7 +5025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>6</v>
       </c>
@@ -4948,7 +5049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>6.9</v>
       </c>
@@ -4972,7 +5073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>6.7</v>
       </c>
@@ -4996,7 +5097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>6.9</v>
       </c>
@@ -5020,7 +5121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>5.8</v>
       </c>
@@ -5044,7 +5145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>6.8</v>
       </c>
@@ -5068,7 +5169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>6.7</v>
       </c>
@@ -5092,7 +5193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>6.7</v>
       </c>
@@ -5116,7 +5217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>6.3</v>
       </c>
@@ -5140,7 +5241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>6.5</v>
       </c>
@@ -5164,7 +5265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>6.2</v>
       </c>
@@ -5188,7 +5289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>5.9</v>
       </c>
@@ -5221,7 +5322,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5231,7 +5332,7 @@
     <col min="8" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
@@ -5263,7 +5364,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -5303,7 +5404,7 @@
         <v>0.40000000000000036</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -5323,7 +5424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5343,7 +5444,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -5363,7 +5464,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -5383,7 +5484,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -5403,7 +5504,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -5423,7 +5524,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5443,7 +5544,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -5463,7 +5564,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -5483,7 +5584,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -5503,7 +5604,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -5523,19 +5624,19 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="9" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5546,9 +5647,55 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="70.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O155"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5557,12 +5704,12 @@
     <col min="5" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75">
+    <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>32</v>
       </c>
@@ -5570,7 +5717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="90">
+    <row r="4" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="N4" s="6" t="s">
         <v>33</v>
       </c>
@@ -5578,7 +5725,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
@@ -5601,7 +5748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,1,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -5631,7 +5778,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,2,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -5645,7 +5792,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,3,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.3</v>
@@ -5659,7 +5806,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,4,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -5673,7 +5820,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,5,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -5687,7 +5834,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,6,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.7</v>
@@ -5701,7 +5848,7 @@
         <v>0.11864406779661016</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,7,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -5715,7 +5862,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,8,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -5729,7 +5876,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,9,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -5743,7 +5890,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,10,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -5757,7 +5904,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,11,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -5771,7 +5918,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,12,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.6</v>
@@ -5785,7 +5932,7 @@
         <v>0.10169491525423729</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,13,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -5799,7 +5946,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,14,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.1000000000000001</v>
@@ -5813,7 +5960,7 @@
         <v>1.6949152542372895E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,15,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.2</v>
@@ -5827,7 +5974,7 @@
         <v>3.3898305084745756E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,16,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -5841,7 +5988,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,17,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.3</v>
@@ -5855,7 +6002,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,18,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -5869,7 +6016,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,19,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.7</v>
@@ -5883,7 +6030,7 @@
         <v>0.11864406779661016</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,20,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -5897,7 +6044,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,21,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.7</v>
@@ -5911,7 +6058,7 @@
         <v>0.11864406779661016</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,22,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -5925,7 +6072,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,23,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1</v>
@@ -5939,7 +6086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,24,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.7</v>
@@ -5953,7 +6100,7 @@
         <v>0.11864406779661016</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,25,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.9</v>
@@ -5967,7 +6114,7 @@
         <v>0.15254237288135591</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,26,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.6</v>
@@ -5981,7 +6128,7 @@
         <v>0.10169491525423729</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,27,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.6</v>
@@ -5995,7 +6142,7 @@
         <v>0.10169491525423729</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,28,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -6009,7 +6156,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,29,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -6023,7 +6170,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,30,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.6</v>
@@ -6037,7 +6184,7 @@
         <v>0.10169491525423729</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,31,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.6</v>
@@ -6051,7 +6198,7 @@
         <v>0.10169491525423729</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,32,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -6065,7 +6212,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,33,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -6079,7 +6226,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,34,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -6093,7 +6240,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,35,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -6107,7 +6254,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,36,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.2</v>
@@ -6121,7 +6268,7 @@
         <v>3.3898305084745756E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,37,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.3</v>
@@ -6135,7 +6282,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,38,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -6149,7 +6296,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,39,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.3</v>
@@ -6163,7 +6310,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,40,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -6177,7 +6324,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,41,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.3</v>
@@ -6191,7 +6338,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,42,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.3</v>
@@ -6205,7 +6352,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,43,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.3</v>
@@ -6219,7 +6366,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,44,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.6</v>
@@ -6233,7 +6380,7 @@
         <v>0.10169491525423729</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,45,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.9</v>
@@ -6247,7 +6394,7 @@
         <v>0.15254237288135591</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,46,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -6261,7 +6408,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,47,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.6</v>
@@ -6275,7 +6422,7 @@
         <v>0.10169491525423729</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,48,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -6289,7 +6436,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,49,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.5</v>
@@ -6303,7 +6450,7 @@
         <v>8.4745762711864403E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,50,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>1.4</v>
@@ -6317,7 +6464,7 @@
         <v>6.7796610169491511E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,51,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.7</v>
@@ -6331,7 +6478,7 @@
         <v>0.6271186440677966</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,52,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -6345,7 +6492,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,53,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -6359,7 +6506,7 @@
         <v>0.66101694915254239</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,54,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4</v>
@@ -6373,7 +6520,7 @@
         <v>0.50847457627118642</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,55,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5999999999999996</v>
@@ -6387,7 +6534,7 @@
         <v>0.61016949152542366</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,56,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -6401,7 +6548,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,57,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.7</v>
@@ -6415,7 +6562,7 @@
         <v>0.6271186440677966</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,58,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.3</v>
@@ -6429,7 +6576,7 @@
         <v>0.38983050847457623</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,59,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5999999999999996</v>
@@ -6443,7 +6590,7 @@
         <v>0.61016949152542366</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,60,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.9</v>
@@ -6457,7 +6604,7 @@
         <v>0.49152542372881353</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,61,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.5</v>
@@ -6471,7 +6618,7 @@
         <v>0.42372881355932202</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,62,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.2</v>
@@ -6485,7 +6632,7 @@
         <v>0.5423728813559322</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,63,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4</v>
@@ -6499,7 +6646,7 @@
         <v>0.50847457627118642</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,64,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.7</v>
@@ -6513,7 +6660,7 @@
         <v>0.6271186440677966</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,65,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.6</v>
@@ -6527,7 +6674,7 @@
         <v>0.44067796610169491</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,66,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.4000000000000004</v>
@@ -6541,7 +6688,7 @@
         <v>0.57627118644067798</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,67,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -6555,7 +6702,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,68,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.0999999999999996</v>
@@ -6569,7 +6716,7 @@
         <v>0.52542372881355925</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,69,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -6583,7 +6730,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,70,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.9</v>
@@ -6597,7 +6744,7 @@
         <v>0.49152542372881353</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,71,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
@@ -6611,7 +6758,7 @@
         <v>0.64406779661016944</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,72,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4</v>
@@ -6625,7 +6772,7 @@
         <v>0.50847457627118642</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,73,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -6639,7 +6786,7 @@
         <v>0.66101694915254239</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,74,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.7</v>
@@ -6653,7 +6800,7 @@
         <v>0.6271186440677966</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,75,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.3</v>
@@ -6667,7 +6814,7 @@
         <v>0.55932203389830504</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,76,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.4000000000000004</v>
@@ -6681,7 +6828,7 @@
         <v>0.57627118644067798</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,77,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
@@ -6695,7 +6842,7 @@
         <v>0.64406779661016944</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,78,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -6709,7 +6856,7 @@
         <v>0.67796610169491522</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,79,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -6723,7 +6870,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,80,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.5</v>
@@ -6737,7 +6884,7 @@
         <v>0.42372881355932202</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,81,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.8</v>
@@ -6751,7 +6898,7 @@
         <v>0.47457627118644063</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,82,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.7</v>
@@ -6765,7 +6912,7 @@
         <v>0.4576271186440678</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,83,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.9</v>
@@ -6779,7 +6926,7 @@
         <v>0.49152542372881353</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,84,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -6793,7 +6940,7 @@
         <v>0.69491525423728806</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,85,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -6807,7 +6954,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,86,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -6821,7 +6968,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,87,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.7</v>
@@ -6835,7 +6982,7 @@
         <v>0.6271186440677966</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,88,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.4000000000000004</v>
@@ -6849,7 +6996,7 @@
         <v>0.57627118644067798</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,89,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.0999999999999996</v>
@@ -6863,7 +7010,7 @@
         <v>0.52542372881355925</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,90,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4</v>
@@ -6877,7 +7024,7 @@
         <v>0.50847457627118642</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,91,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.4000000000000004</v>
@@ -6891,7 +7038,7 @@
         <v>0.57627118644067798</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,92,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5999999999999996</v>
@@ -6905,7 +7052,7 @@
         <v>0.61016949152542366</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,93,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4</v>
@@ -6919,7 +7066,7 @@
         <v>0.50847457627118642</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,94,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3.3</v>
@@ -6933,7 +7080,7 @@
         <v>0.38983050847457623</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,95,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.2</v>
@@ -6947,7 +7094,7 @@
         <v>0.5423728813559322</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,96,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.2</v>
@@ -6961,7 +7108,7 @@
         <v>0.5423728813559322</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,97,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.2</v>
@@ -6975,7 +7122,7 @@
         <v>0.5423728813559322</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,98,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.3</v>
@@ -6989,7 +7136,7 @@
         <v>0.55932203389830504</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,99,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>3</v>
@@ -7003,7 +7150,7 @@
         <v>0.33898305084745761</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,100,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.0999999999999996</v>
@@ -7017,7 +7164,7 @@
         <v>0.52542372881355925</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,101,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -7031,7 +7178,7 @@
         <v>0.84745762711864403</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,102,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7045,7 +7192,7 @@
         <v>0.69491525423728806</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,103,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.9</v>
@@ -7059,7 +7206,7 @@
         <v>0.83050847457627119</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,104,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -7073,7 +7220,7 @@
         <v>0.77966101694915246</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,105,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -7087,7 +7234,7 @@
         <v>0.81355932203389825</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,106,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.6</v>
@@ -7101,7 +7248,7 @@
         <v>0.94915254237288127</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,107,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -7115,7 +7262,7 @@
         <v>0.59322033898305082</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,108,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -7129,7 +7276,7 @@
         <v>0.89830508474576265</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,109,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -7143,7 +7290,7 @@
         <v>0.81355932203389825</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,110,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -7157,7 +7304,7 @@
         <v>0.86440677966101687</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,111,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7171,7 +7318,7 @@
         <v>0.69491525423728806</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,112,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.3</v>
@@ -7185,7 +7332,7 @@
         <v>0.72881355932203384</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,113,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -7199,7 +7346,7 @@
         <v>0.76271186440677963</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,114,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -7213,7 +7360,7 @@
         <v>0.67796610169491522</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,115,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7227,7 +7374,7 @@
         <v>0.69491525423728806</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,116,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.3</v>
@@ -7241,7 +7388,7 @@
         <v>0.72881355932203384</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,117,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -7255,7 +7402,7 @@
         <v>0.76271186440677963</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,118,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -7269,7 +7416,7 @@
         <v>0.96610169491525422</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,119,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.9</v>
@@ -7283,7 +7430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,120,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -7297,7 +7444,7 @@
         <v>0.67796610169491522</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,121,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -7311,7 +7458,7 @@
         <v>0.79661016949152541</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,122,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -7325,7 +7472,7 @@
         <v>0.66101694915254239</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,123,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -7339,7 +7486,7 @@
         <v>0.96610169491525422</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,124,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -7353,7 +7500,7 @@
         <v>0.66101694915254239</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,125,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -7367,7 +7514,7 @@
         <v>0.79661016949152541</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,126,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -7381,7 +7528,7 @@
         <v>0.84745762711864403</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,127,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
@@ -7395,7 +7542,7 @@
         <v>0.64406779661016944</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,128,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -7409,7 +7556,7 @@
         <v>0.66101694915254239</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,129,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -7423,7 +7570,7 @@
         <v>0.77966101694915246</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,130,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -7437,7 +7584,7 @@
         <v>0.81355932203389825</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,131,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -7451,7 +7598,7 @@
         <v>0.86440677966101687</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,132,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -7465,7 +7612,7 @@
         <v>0.9152542372881356</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,133,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -7479,7 +7626,7 @@
         <v>0.77966101694915246</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,134,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7493,7 +7640,7 @@
         <v>0.69491525423728806</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,135,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -7507,7 +7654,7 @@
         <v>0.77966101694915246</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,136,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -7521,7 +7668,7 @@
         <v>0.86440677966101687</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,137,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -7535,7 +7682,7 @@
         <v>0.77966101694915246</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,138,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -7549,7 +7696,7 @@
         <v>0.76271186440677963</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,139,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
@@ -7563,7 +7710,7 @@
         <v>0.64406779661016944</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,140,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
@@ -7577,7 +7724,7 @@
         <v>0.74576271186440679</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,141,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -7591,7 +7738,7 @@
         <v>0.77966101694915246</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,142,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7605,7 +7752,7 @@
         <v>0.69491525423728806</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,143,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7619,7 +7766,7 @@
         <v>0.69491525423728806</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,144,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.9</v>
@@ -7633,7 +7780,7 @@
         <v>0.83050847457627119</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,145,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -7647,7 +7794,7 @@
         <v>0.79661016949152541</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,146,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.2</v>
@@ -7661,7 +7808,7 @@
         <v>0.71186440677966101</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,147,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -7675,7 +7822,7 @@
         <v>0.67796610169491522</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,148,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.2</v>
@@ -7689,7 +7836,7 @@
         <v>0.71186440677966101</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,149,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
@@ -7703,7 +7850,7 @@
         <v>0.74576271186440679</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,150,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7722,22 +7869,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I154"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -7745,7 +7892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -7774,7 +7921,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,1,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -7800,7 +7947,7 @@
         <v>8.3500000000000014</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" ref="G5:G36" si="0">IF(OR(A5&lt;$E$5,A5&gt;$F$5),"YES","NO")</f>
+        <f>IF(OR(A5&lt;$E$5,A5&gt;$F$5),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="H5">
@@ -7808,17 +7955,17 @@
         <v>-0.89767387919678832</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I36" si="1">IF(ABS(H5)&gt;3,"YES","NO")</f>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <f t="shared" ref="I5:I36" si="0">IF(ABS(H5)&gt;3,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,2,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G6:G36" si="1">IF(OR(A6&lt;$E$5,A6&gt;$F$5),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="H6">
@@ -7826,17 +7973,17 @@
         <v>-1.1392004834649812</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,3,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.7</v>
       </c>
       <c r="G7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H7">
@@ -7844,17 +7991,17 @@
         <v>-1.380727087733175</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,4,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H8">
@@ -7862,17 +8009,17 @@
         <v>-1.5014903898672725</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,5,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
       </c>
       <c r="G9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H9">
@@ -7880,17 +8027,17 @@
         <v>-1.0184371813308848</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,6,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
       </c>
       <c r="G10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H10">
@@ -7898,17 +8045,17 @@
         <v>-0.53538397279449701</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,7,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="G11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H11">
@@ -7916,17 +8063,17 @@
         <v>-1.5014903898672725</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,8,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
       </c>
       <c r="G12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H12">
@@ -7934,17 +8081,17 @@
         <v>-1.0184371813308848</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,9,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="G13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H13">
@@ -7952,17 +8099,17 @@
         <v>-1.7430169941354652</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,10,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H14">
@@ -7970,17 +8117,17 @@
         <v>-1.1392004834649812</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,11,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H15">
@@ -7988,17 +8135,17 @@
         <v>-0.53538397279449701</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,12,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H16">
@@ -8006,17 +8153,17 @@
         <v>-1.2599637855990786</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,13,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H17">
@@ -8024,17 +8171,17 @@
         <v>-1.2599637855990786</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,14,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.3</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H18">
@@ -8042,17 +8189,17 @@
         <v>-1.8637802962695627</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,15,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H19">
@@ -8060,17 +8207,17 @@
         <v>-5.2330764258110368E-2</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,16,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H20">
@@ -8078,17 +8225,17 @@
         <v>-0.17309406639220676</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,17,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H21">
@@ -8096,17 +8243,17 @@
         <v>-0.53538397279449701</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,18,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H22">
@@ -8114,17 +8261,17 @@
         <v>-0.89767387919678832</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,19,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H23">
@@ -8132,17 +8279,17 @@
         <v>-0.17309406639220676</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,20,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H24">
@@ -8150,17 +8297,17 @@
         <v>-0.89767387919678832</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,21,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H25">
@@ -8168,17 +8315,17 @@
         <v>-0.53538397279449701</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,22,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H26">
@@ -8186,17 +8333,17 @@
         <v>-0.89767387919678832</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,23,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H27">
@@ -8204,17 +8351,17 @@
         <v>-1.5014903898672725</v>
       </c>
       <c r="I27" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,24,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H28">
@@ -8222,17 +8369,17 @@
         <v>-0.89767387919678832</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,25,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H29">
@@ -8240,17 +8387,17 @@
         <v>-1.2599637855990786</v>
       </c>
       <c r="I29" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,26,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H30">
@@ -8258,17 +8405,17 @@
         <v>-1.0184371813308848</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,27,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H31">
@@ -8276,17 +8423,17 @@
         <v>-1.0184371813308848</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,28,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.2</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H32">
@@ -8294,17 +8441,17 @@
         <v>-0.77691057706269084</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,29,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.2</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H33">
@@ -8312,17 +8459,17 @@
         <v>-0.77691057706269084</v>
       </c>
       <c r="I33" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,30,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.7</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H34">
@@ -8330,17 +8477,17 @@
         <v>-1.380727087733175</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,31,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H35">
@@ -8348,17 +8495,17 @@
         <v>-1.2599637855990786</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,32,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NO</v>
       </c>
       <c r="H36">
@@ -8366,11 +8513,11 @@
         <v>-0.53538397279449701</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="1"/>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,33,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.2</v>
@@ -8388,7 +8535,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,34,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -8406,7 +8553,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,35,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -8424,7 +8571,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,36,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -8442,7 +8589,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,37,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -8460,7 +8607,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,38,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -8478,7 +8625,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,39,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.4000000000000004</v>
@@ -8496,7 +8643,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,40,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -8514,7 +8661,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,41,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -8532,7 +8679,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,42,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5</v>
@@ -8550,7 +8697,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,43,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.4000000000000004</v>
@@ -8568,7 +8715,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,44,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -8586,7 +8733,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,45,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -8604,7 +8751,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,46,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.8</v>
@@ -8622,7 +8769,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,47,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -8640,7 +8787,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,48,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.5999999999999996</v>
@@ -8658,7 +8805,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,49,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.3</v>
@@ -8676,7 +8823,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,50,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -8694,7 +8841,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,51,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7</v>
@@ -8712,7 +8859,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,52,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -8730,7 +8877,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,53,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.9</v>
@@ -8748,7 +8895,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,54,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -8766,7 +8913,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,55,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.5</v>
@@ -8784,7 +8931,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,56,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -8802,7 +8949,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,57,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -8820,7 +8967,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,58,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -8838,7 +8985,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,59,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.6</v>
@@ -8856,7 +9003,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,60,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.2</v>
@@ -8874,7 +9021,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,61,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -8892,7 +9039,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,62,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.9</v>
@@ -8910,7 +9057,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,63,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -8928,7 +9075,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,64,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -8946,7 +9093,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,65,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -8964,7 +9111,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,66,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -8982,7 +9129,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,67,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -9000,7 +9147,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,68,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -9018,7 +9165,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,69,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.2</v>
@@ -9036,7 +9183,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,70,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -9054,7 +9201,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,71,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.9</v>
@@ -9072,7 +9219,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,72,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -9090,7 +9237,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,73,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -9108,7 +9255,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,74,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -9126,7 +9273,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,75,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -9144,7 +9291,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,76,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.6</v>
@@ -9162,7 +9309,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,77,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.8</v>
@@ -9180,7 +9327,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,78,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -9198,7 +9345,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,79,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -9216,7 +9363,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,80,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -9234,7 +9381,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,81,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -9252,7 +9399,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,82,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -9270,7 +9417,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,83,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -9288,7 +9435,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,84,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -9306,7 +9453,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,85,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.4</v>
@@ -9324,7 +9471,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,86,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -9342,7 +9489,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,87,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -9360,7 +9507,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,88,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -9378,7 +9525,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,89,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -9396,7 +9543,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,90,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -9414,7 +9561,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,91,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.5</v>
@@ -9432,7 +9579,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,92,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -9450,7 +9597,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,93,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -9468,7 +9615,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,94,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5</v>
@@ -9486,7 +9633,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,95,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -9504,7 +9651,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,96,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -9522,7 +9669,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,97,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -9540,7 +9687,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,98,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.2</v>
@@ -9558,7 +9705,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,99,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.0999999999999996</v>
@@ -9576,7 +9723,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,100,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -9594,7 +9741,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,101,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -9612,7 +9759,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,102,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -9630,7 +9777,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,103,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.1</v>
@@ -9648,7 +9795,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,104,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -9666,7 +9813,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,105,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.5</v>
@@ -9684,7 +9831,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,106,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.6</v>
@@ -9702,7 +9849,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,107,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>4.9000000000000004</v>
@@ -9720,7 +9867,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,108,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.3</v>
@@ -9738,7 +9885,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,109,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -9756,7 +9903,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,110,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.2</v>
@@ -9774,7 +9921,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,111,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.5</v>
@@ -9792,7 +9939,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,112,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -9810,7 +9957,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,113,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.8</v>
@@ -9828,7 +9975,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,114,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.7</v>
@@ -9846,7 +9993,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,115,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -9864,7 +10011,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,116,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -9882,7 +10029,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,117,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.5</v>
@@ -9900,7 +10047,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,118,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.7</v>
@@ -9918,7 +10065,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,119,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.7</v>
@@ -9936,7 +10083,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,120,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -9954,7 +10101,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,121,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.9</v>
@@ -9972,7 +10119,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,122,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.6</v>
@@ -9990,7 +10137,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,123,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.7</v>
@@ -10008,7 +10155,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,124,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -10026,7 +10173,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,125,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -10044,7 +10191,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,126,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.2</v>
@@ -10062,7 +10209,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,127,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.2</v>
@@ -10080,7 +10227,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,128,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -10098,7 +10245,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,129,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -10116,7 +10263,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,130,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.2</v>
@@ -10134,7 +10281,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,131,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.4</v>
@@ -10152,7 +10299,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,132,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.9</v>
@@ -10170,7 +10317,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,133,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -10188,7 +10335,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,134,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -10206,7 +10353,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,135,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.1</v>
@@ -10224,7 +10371,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,136,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>7.7</v>
@@ -10242,7 +10389,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,137,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -10260,7 +10407,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,138,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.4</v>
@@ -10278,7 +10425,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,139,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6</v>
@@ -10296,7 +10443,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,140,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.9</v>
@@ -10314,7 +10461,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,141,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -10332,7 +10479,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,142,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.9</v>
@@ -10350,7 +10497,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,143,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.8</v>
@@ -10368,7 +10515,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,144,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.8</v>
@@ -10386,7 +10533,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,145,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -10404,7 +10551,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,146,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.7</v>
@@ -10422,7 +10569,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,147,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.3</v>
@@ -10440,7 +10587,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,148,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.5</v>
@@ -10458,7 +10605,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,149,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>6.2</v>
@@ -10476,7 +10623,7 @@
         <v>NO</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <f>INDEX(Dati_grezzi!$A$2:$D$151,150,MATCH($B$3,Dati_grezzi!$A$1:$D$1,0))</f>
         <v>5.9</v>
@@ -10500,65 +10647,574 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E32CF21-0BFF-4609-807B-E20BDED60E91}">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
-        <v>50</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="70.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96728C41-8E02-447C-B88F-59C6DBB20D94}">
-  <dimension ref="A3:E21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A2:E22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>53</v>
       </c>
@@ -10566,7 +11222,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>55</v>
       </c>
@@ -10583,180 +11239,147 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C5">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13">
         <v>50</v>
       </c>
-      <c r="E5">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>46</v>
-      </c>
-      <c r="E6">
+      <c r="B6" s="13">
+        <v>2</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13">
+        <v>48</v>
+      </c>
+      <c r="E6" s="13">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B7">
-        <v>47</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
+      <c r="B7" s="13">
+        <v>44</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13">
+        <v>6</v>
+      </c>
+      <c r="E7" s="13">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B8">
-        <v>51</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="13">
+        <v>46</v>
+      </c>
+      <c r="C8" s="13">
         <v>50</v>
       </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
+      <c r="D8" s="13">
+        <v>54</v>
+      </c>
+      <c r="E8" s="13">
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
         <f>$E5*B$8/$E$8</f>
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <f t="shared" ref="B11:C11" si="0">$E5*C$8/$E$8</f>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="B12">
+        <f>$E5*C$8/$E$8</f>
         <v>16.666666666666668</v>
       </c>
-      <c r="C11">
+      <c r="C12">
+        <f>$E5*D$8/$E$8</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f>$E6*B$8/$E$8</f>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ref="B13:C13" si="0">$E6*C$8/$E$8</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="C13">
         <f t="shared" si="0"/>
-        <v>16.333333333333332</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <f>$E6*B$8/$E$8</f>
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <f t="shared" ref="B12:C12" si="1">$E6*C$8/$E$8</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" ref="A14:C14" si="1">$E7*B$8/$E$8</f>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="1"/>
         <v>16.666666666666668</v>
       </c>
-      <c r="C12">
+      <c r="C14">
         <f t="shared" si="1"/>
-        <v>16.333333333333332</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <f t="shared" ref="A12:C13" si="2">$E7*B$8/$E$8</f>
-        <v>17</v>
-      </c>
-      <c r="B13">
-        <f t="shared" si="2"/>
-        <v>16.666666666666668</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="2"/>
-        <v>16.333333333333332</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f>_xlfn.CHISQ.TEST(B5:D7,A12:C14)</f>
+        <v>5.6942708958950342E-40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20">
-        <f>_xlfn.CHISQ.TEST(B5:D7,A11:C13)</f>
-        <v>6.2570729137711216E-41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -10771,15 +11394,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010065D4BF43CB49E94486AE0BDB12F2F219" ma:contentTypeVersion="10" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="24552c6a2e8d14f430877fa013599989">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="674b27b8-e1cd-4723-9694-0b904cc35f92" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6b84a6e24a18f569593973411257d8" ns2:_="">
     <xsd:import namespace="674b27b8-e1cd-4723-9694-0b904cc35f92"/>
@@ -10957,14 +11571,47 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9910A44-9D4B-4AE0-8F32-468CD0F680ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9910A44-9D4B-4AE0-8F32-468CD0F680ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="674b27b8-e1cd-4723-9694-0b904cc35f92"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAACB6A-3780-4878-A77A-6EE417743D34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ACF5F39-A1FC-4396-8534-8482C8819197}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="674b27b8-e1cd-4723-9694-0b904cc35f92"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ACF5F39-A1FC-4396-8534-8482C8819197}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAACB6A-3780-4878-A77A-6EE417743D34}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Lezione 1 - Iris_Lab_Excel.xlsx
+++ b/Lezione 1 - Iris_Lab_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmorelli\IdeaProjects\B3099---LABORATORIO-DI-OTTIMIZZAZIONE-INTELLIGENZA-ARTIFICIALE-E-MACHINE-LEARNING---2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CAD2D0-D190-4F57-A666-CFDA9C061E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53270896-6B7C-4F72-A55B-92FE16D0F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,8 @@
     <sheet name="Scatter" sheetId="6" r:id="rId5"/>
     <sheet name="Preprocessing" sheetId="4" r:id="rId6"/>
     <sheet name="Outlier_IQR" sheetId="5" r:id="rId7"/>
-    <sheet name="Dettagli1" sheetId="12" r:id="rId8"/>
-    <sheet name="Chi Quadro" sheetId="11" r:id="rId9"/>
-    <sheet name="Consegna" sheetId="8" r:id="rId10"/>
+    <sheet name="Chi Quadro" sheetId="11" r:id="rId8"/>
+    <sheet name="Consegna" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dati_grezzi!$A$1:$E$151</definedName>
@@ -30,7 +29,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -52,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="76">
   <si>
     <t>Laboratorio 1 – Iris (Excel 365, IT)</t>
   </si>
@@ -282,9 +281,6 @@
   <si>
     <t>Test T</t>
   </si>
-  <si>
-    <t>Dettagli per Somma di Contatore - species: virginica, bin: Alto</t>
-  </si>
 </sst>
 </file>
 
@@ -353,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -377,7 +373,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1183,7 +1178,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30BC0138-36EC-407B-9CFD-362C426E4BE0}" name="Tabella pivot2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30BC0138-36EC-407B-9CFD-362C426E4BE0}" name="Tabella pivot2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -1251,18 +1246,6 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{54BDAE5D-A46C-4D6C-AC97-7707B981486E}" name="Tabella1" displayName="Tabella1" ref="A3:C50" totalsRowShown="0">
-  <autoFilter ref="A3:C50" xr:uid="{54BDAE5D-A46C-4D6C-AC97-7707B981486E}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{833068E0-2309-4183-98A7-7FBCA329A4D3}" name="species"/>
-    <tableColumn id="2" xr3:uid="{8B1BE7E6-6C4E-46F7-966C-58C1023B6EEA}" name="bin"/>
-    <tableColumn id="3" xr3:uid="{AD18D3FE-4A6B-4168-BA91-4CB7D5B4CBC2}" name="Contatore"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1606,57 +1589,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1668,11 +1603,10 @@
     <col min="7" max="7" width="12.28515625" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="1.85546875" customWidth="1"/>
-    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -1697,11 +1631,11 @@
       <c r="I1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="O1" t="s">
+      <c r="J1" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5.0999999999999996</v>
       </c>
@@ -1718,7 +1652,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="str">
-        <f>IF(Dati_grezzi!C2&lt;=$O$2,"Basso",IF(C2&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C2&lt;=$J$2,"Basso",IF(C2&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G2">
@@ -1728,12 +1662,12 @@
         <f>TTEST(C2:C51,C52:C101,2,3)</f>
         <v>9.9344329575875926E-46</v>
       </c>
-      <c r="O2">
+      <c r="J2">
         <f>_xlfn.PERCENTILE.INC(Dati_grezzi!C2:C151,0.3333)</f>
         <v>2.6278699999999957</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4.9000000000000004</v>
       </c>
@@ -1750,18 +1684,18 @@
         <v>17</v>
       </c>
       <c r="F3" t="str">
-        <f>IF(Dati_grezzi!C3&lt;=$O$2,"Basso",IF(C3&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C3&lt;=$J$2,"Basso",IF(C3&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="O3">
+      <c r="J3">
         <f>_xlfn.PERCENTILE.INC(Dati_grezzi!C2:C151,0.66666)</f>
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4.7</v>
       </c>
@@ -1778,14 +1712,14 @@
         <v>17</v>
       </c>
       <c r="F4" t="str">
-        <f>IF(Dati_grezzi!C4&lt;=$O$2,"Basso",IF(C4&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C4&lt;=$J$2,"Basso",IF(C4&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4.5999999999999996</v>
       </c>
@@ -1802,14 +1736,14 @@
         <v>17</v>
       </c>
       <c r="F5" t="str">
-        <f>IF(Dati_grezzi!C5&lt;=$O$2,"Basso",IF(C5&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C5&lt;=$J$2,"Basso",IF(C5&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1826,14 +1760,14 @@
         <v>17</v>
       </c>
       <c r="F6" t="str">
-        <f>IF(Dati_grezzi!C6&lt;=$O$2,"Basso",IF(C6&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C6&lt;=$J$2,"Basso",IF(C6&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5.4</v>
       </c>
@@ -1850,14 +1784,14 @@
         <v>17</v>
       </c>
       <c r="F7" t="str">
-        <f>IF(Dati_grezzi!C7&lt;=$O$2,"Basso",IF(C7&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C7&lt;=$J$2,"Basso",IF(C7&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4.5999999999999996</v>
       </c>
@@ -1874,14 +1808,14 @@
         <v>17</v>
       </c>
       <c r="F8" t="str">
-        <f>IF(Dati_grezzi!C8&lt;=$O$2,"Basso",IF(C8&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C8&lt;=$J$2,"Basso",IF(C8&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1898,14 +1832,14 @@
         <v>17</v>
       </c>
       <c r="F9" t="str">
-        <f>IF(Dati_grezzi!C9&lt;=$O$2,"Basso",IF(C9&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C9&lt;=$J$2,"Basso",IF(C9&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>4.4000000000000004</v>
       </c>
@@ -1922,14 +1856,14 @@
         <v>17</v>
       </c>
       <c r="F10" t="str">
-        <f>IF(Dati_grezzi!C10&lt;=$O$2,"Basso",IF(C10&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C10&lt;=$J$2,"Basso",IF(C10&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>4.9000000000000004</v>
       </c>
@@ -1946,14 +1880,14 @@
         <v>17</v>
       </c>
       <c r="F11" t="str">
-        <f>IF(Dati_grezzi!C11&lt;=$O$2,"Basso",IF(C11&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C11&lt;=$J$2,"Basso",IF(C11&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5.4</v>
       </c>
@@ -1970,14 +1904,14 @@
         <v>17</v>
       </c>
       <c r="F12" t="str">
-        <f>IF(Dati_grezzi!C12&lt;=$O$2,"Basso",IF(C12&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C12&lt;=$J$2,"Basso",IF(C12&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4.8</v>
       </c>
@@ -1994,14 +1928,14 @@
         <v>17</v>
       </c>
       <c r="F13" t="str">
-        <f>IF(Dati_grezzi!C13&lt;=$O$2,"Basso",IF(C13&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C13&lt;=$J$2,"Basso",IF(C13&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4.8</v>
       </c>
@@ -2018,14 +1952,14 @@
         <v>17</v>
       </c>
       <c r="F14" t="str">
-        <f>IF(Dati_grezzi!C14&lt;=$O$2,"Basso",IF(C14&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C14&lt;=$J$2,"Basso",IF(C14&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4.3</v>
       </c>
@@ -2042,14 +1976,14 @@
         <v>17</v>
       </c>
       <c r="F15" t="str">
-        <f>IF(Dati_grezzi!C15&lt;=$O$2,"Basso",IF(C15&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C15&lt;=$J$2,"Basso",IF(C15&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>5.8</v>
       </c>
@@ -2066,7 +2000,7 @@
         <v>17</v>
       </c>
       <c r="F16" t="str">
-        <f>IF(Dati_grezzi!C16&lt;=$O$2,"Basso",IF(C16&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C16&lt;=$J$2,"Basso",IF(C16&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G16">
@@ -2090,7 +2024,7 @@
         <v>17</v>
       </c>
       <c r="F17" t="str">
-        <f>IF(Dati_grezzi!C17&lt;=$O$2,"Basso",IF(C17&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C17&lt;=$J$2,"Basso",IF(C17&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G17">
@@ -2114,7 +2048,7 @@
         <v>17</v>
       </c>
       <c r="F18" t="str">
-        <f>IF(Dati_grezzi!C18&lt;=$O$2,"Basso",IF(C18&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C18&lt;=$J$2,"Basso",IF(C18&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G18">
@@ -2138,7 +2072,7 @@
         <v>17</v>
       </c>
       <c r="F19" t="str">
-        <f>IF(Dati_grezzi!C19&lt;=$O$2,"Basso",IF(C19&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C19&lt;=$J$2,"Basso",IF(C19&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G19">
@@ -2162,7 +2096,7 @@
         <v>17</v>
       </c>
       <c r="F20" t="str">
-        <f>IF(Dati_grezzi!C20&lt;=$O$2,"Basso",IF(C20&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C20&lt;=$J$2,"Basso",IF(C20&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G20">
@@ -2186,7 +2120,7 @@
         <v>17</v>
       </c>
       <c r="F21" t="str">
-        <f>IF(Dati_grezzi!C21&lt;=$O$2,"Basso",IF(C21&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C21&lt;=$J$2,"Basso",IF(C21&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G21">
@@ -2210,7 +2144,7 @@
         <v>17</v>
       </c>
       <c r="F22" t="str">
-        <f>IF(Dati_grezzi!C22&lt;=$O$2,"Basso",IF(C22&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C22&lt;=$J$2,"Basso",IF(C22&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G22">
@@ -2234,7 +2168,7 @@
         <v>17</v>
       </c>
       <c r="F23" t="str">
-        <f>IF(Dati_grezzi!C23&lt;=$O$2,"Basso",IF(C23&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C23&lt;=$J$2,"Basso",IF(C23&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G23">
@@ -2258,7 +2192,7 @@
         <v>17</v>
       </c>
       <c r="F24" t="str">
-        <f>IF(Dati_grezzi!C24&lt;=$O$2,"Basso",IF(C24&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C24&lt;=$J$2,"Basso",IF(C24&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G24">
@@ -2282,7 +2216,7 @@
         <v>17</v>
       </c>
       <c r="F25" t="str">
-        <f>IF(Dati_grezzi!C25&lt;=$O$2,"Basso",IF(C25&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C25&lt;=$J$2,"Basso",IF(C25&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G25">
@@ -2306,7 +2240,7 @@
         <v>17</v>
       </c>
       <c r="F26" t="str">
-        <f>IF(Dati_grezzi!C26&lt;=$O$2,"Basso",IF(C26&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C26&lt;=$J$2,"Basso",IF(C26&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G26">
@@ -2330,7 +2264,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="str">
-        <f>IF(Dati_grezzi!C27&lt;=$O$2,"Basso",IF(C27&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C27&lt;=$J$2,"Basso",IF(C27&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G27">
@@ -2354,7 +2288,7 @@
         <v>17</v>
       </c>
       <c r="F28" t="str">
-        <f>IF(Dati_grezzi!C28&lt;=$O$2,"Basso",IF(C28&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C28&lt;=$J$2,"Basso",IF(C28&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G28">
@@ -2378,7 +2312,7 @@
         <v>17</v>
       </c>
       <c r="F29" t="str">
-        <f>IF(Dati_grezzi!C29&lt;=$O$2,"Basso",IF(C29&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C29&lt;=$J$2,"Basso",IF(C29&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G29">
@@ -2402,7 +2336,7 @@
         <v>17</v>
       </c>
       <c r="F30" t="str">
-        <f>IF(Dati_grezzi!C30&lt;=$O$2,"Basso",IF(C30&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C30&lt;=$J$2,"Basso",IF(C30&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G30">
@@ -2426,7 +2360,7 @@
         <v>17</v>
       </c>
       <c r="F31" t="str">
-        <f>IF(Dati_grezzi!C31&lt;=$O$2,"Basso",IF(C31&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C31&lt;=$J$2,"Basso",IF(C31&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G31">
@@ -2450,7 +2384,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="str">
-        <f>IF(Dati_grezzi!C32&lt;=$O$2,"Basso",IF(C32&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C32&lt;=$J$2,"Basso",IF(C32&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G32">
@@ -2474,7 +2408,7 @@
         <v>17</v>
       </c>
       <c r="F33" t="str">
-        <f>IF(Dati_grezzi!C33&lt;=$O$2,"Basso",IF(C33&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C33&lt;=$J$2,"Basso",IF(C33&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G33">
@@ -2498,7 +2432,7 @@
         <v>17</v>
       </c>
       <c r="F34" t="str">
-        <f>IF(Dati_grezzi!C34&lt;=$O$2,"Basso",IF(C34&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C34&lt;=$J$2,"Basso",IF(C34&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G34">
@@ -2522,7 +2456,7 @@
         <v>17</v>
       </c>
       <c r="F35" t="str">
-        <f>IF(Dati_grezzi!C35&lt;=$O$2,"Basso",IF(C35&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C35&lt;=$J$2,"Basso",IF(C35&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G35">
@@ -2546,7 +2480,7 @@
         <v>17</v>
       </c>
       <c r="F36" t="str">
-        <f>IF(Dati_grezzi!C36&lt;=$O$2,"Basso",IF(C36&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C36&lt;=$J$2,"Basso",IF(C36&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G36">
@@ -2570,7 +2504,7 @@
         <v>17</v>
       </c>
       <c r="F37" t="str">
-        <f>IF(Dati_grezzi!C37&lt;=$O$2,"Basso",IF(C37&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C37&lt;=$J$2,"Basso",IF(C37&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G37">
@@ -2594,7 +2528,7 @@
         <v>17</v>
       </c>
       <c r="F38" t="str">
-        <f>IF(Dati_grezzi!C38&lt;=$O$2,"Basso",IF(C38&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C38&lt;=$J$2,"Basso",IF(C38&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G38">
@@ -2618,7 +2552,7 @@
         <v>17</v>
       </c>
       <c r="F39" t="str">
-        <f>IF(Dati_grezzi!C39&lt;=$O$2,"Basso",IF(C39&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C39&lt;=$J$2,"Basso",IF(C39&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G39">
@@ -2642,7 +2576,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="str">
-        <f>IF(Dati_grezzi!C40&lt;=$O$2,"Basso",IF(C40&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C40&lt;=$J$2,"Basso",IF(C40&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G40">
@@ -2666,7 +2600,7 @@
         <v>17</v>
       </c>
       <c r="F41" t="str">
-        <f>IF(Dati_grezzi!C41&lt;=$O$2,"Basso",IF(C41&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C41&lt;=$J$2,"Basso",IF(C41&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G41">
@@ -2690,7 +2624,7 @@
         <v>17</v>
       </c>
       <c r="F42" t="str">
-        <f>IF(Dati_grezzi!C42&lt;=$O$2,"Basso",IF(C42&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C42&lt;=$J$2,"Basso",IF(C42&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G42">
@@ -2714,7 +2648,7 @@
         <v>17</v>
       </c>
       <c r="F43" t="str">
-        <f>IF(Dati_grezzi!C43&lt;=$O$2,"Basso",IF(C43&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C43&lt;=$J$2,"Basso",IF(C43&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G43">
@@ -2738,7 +2672,7 @@
         <v>17</v>
       </c>
       <c r="F44" t="str">
-        <f>IF(Dati_grezzi!C44&lt;=$O$2,"Basso",IF(C44&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C44&lt;=$J$2,"Basso",IF(C44&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G44">
@@ -2762,7 +2696,7 @@
         <v>17</v>
       </c>
       <c r="F45" t="str">
-        <f>IF(Dati_grezzi!C45&lt;=$O$2,"Basso",IF(C45&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C45&lt;=$J$2,"Basso",IF(C45&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G45">
@@ -2786,7 +2720,7 @@
         <v>17</v>
       </c>
       <c r="F46" t="str">
-        <f>IF(Dati_grezzi!C46&lt;=$O$2,"Basso",IF(C46&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C46&lt;=$J$2,"Basso",IF(C46&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G46">
@@ -2810,7 +2744,7 @@
         <v>17</v>
       </c>
       <c r="F47" t="str">
-        <f>IF(Dati_grezzi!C47&lt;=$O$2,"Basso",IF(C47&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C47&lt;=$J$2,"Basso",IF(C47&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G47">
@@ -2834,7 +2768,7 @@
         <v>17</v>
       </c>
       <c r="F48" t="str">
-        <f>IF(Dati_grezzi!C48&lt;=$O$2,"Basso",IF(C48&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C48&lt;=$J$2,"Basso",IF(C48&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G48">
@@ -2858,7 +2792,7 @@
         <v>17</v>
       </c>
       <c r="F49" t="str">
-        <f>IF(Dati_grezzi!C49&lt;=$O$2,"Basso",IF(C49&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C49&lt;=$J$2,"Basso",IF(C49&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G49">
@@ -2882,7 +2816,7 @@
         <v>17</v>
       </c>
       <c r="F50" t="str">
-        <f>IF(Dati_grezzi!C50&lt;=$O$2,"Basso",IF(C50&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C50&lt;=$J$2,"Basso",IF(C50&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G50">
@@ -2906,7 +2840,7 @@
         <v>17</v>
       </c>
       <c r="F51" t="str">
-        <f>IF(Dati_grezzi!C51&lt;=$O$2,"Basso",IF(C51&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C51&lt;=$J$2,"Basso",IF(C51&lt;=$J$3,"Medio","Alto"))</f>
         <v>Basso</v>
       </c>
       <c r="G51">
@@ -2930,7 +2864,7 @@
         <v>18</v>
       </c>
       <c r="F52" t="str">
-        <f>IF(Dati_grezzi!C52&lt;=$O$2,"Basso",IF(C52&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C52&lt;=$J$2,"Basso",IF(C52&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G52">
@@ -2954,7 +2888,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="str">
-        <f>IF(Dati_grezzi!C53&lt;=$O$2,"Basso",IF(C53&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C53&lt;=$J$2,"Basso",IF(C53&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G53">
@@ -2978,7 +2912,7 @@
         <v>18</v>
       </c>
       <c r="F54" t="str">
-        <f>IF(Dati_grezzi!C54&lt;=$O$2,"Basso",IF(C54&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C54&lt;=$J$2,"Basso",IF(C54&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G54">
@@ -3002,7 +2936,7 @@
         <v>18</v>
       </c>
       <c r="F55" t="str">
-        <f>IF(Dati_grezzi!C55&lt;=$O$2,"Basso",IF(C55&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C55&lt;=$J$2,"Basso",IF(C55&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G55">
@@ -3026,7 +2960,7 @@
         <v>18</v>
       </c>
       <c r="F56" t="str">
-        <f>IF(Dati_grezzi!C56&lt;=$O$2,"Basso",IF(C56&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C56&lt;=$J$2,"Basso",IF(C56&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G56">
@@ -3050,7 +2984,7 @@
         <v>18</v>
       </c>
       <c r="F57" t="str">
-        <f>IF(Dati_grezzi!C57&lt;=$O$2,"Basso",IF(C57&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C57&lt;=$J$2,"Basso",IF(C57&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G57">
@@ -3074,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="F58" t="str">
-        <f>IF(Dati_grezzi!C58&lt;=$O$2,"Basso",IF(C58&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C58&lt;=$J$2,"Basso",IF(C58&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G58">
@@ -3098,7 +3032,7 @@
         <v>18</v>
       </c>
       <c r="F59" t="str">
-        <f>IF(Dati_grezzi!C59&lt;=$O$2,"Basso",IF(C59&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C59&lt;=$J$2,"Basso",IF(C59&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G59">
@@ -3122,7 +3056,7 @@
         <v>18</v>
       </c>
       <c r="F60" t="str">
-        <f>IF(Dati_grezzi!C60&lt;=$O$2,"Basso",IF(C60&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C60&lt;=$J$2,"Basso",IF(C60&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G60">
@@ -3146,7 +3080,7 @@
         <v>18</v>
       </c>
       <c r="F61" t="str">
-        <f>IF(Dati_grezzi!C61&lt;=$O$2,"Basso",IF(C61&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C61&lt;=$J$2,"Basso",IF(C61&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G61">
@@ -3170,7 +3104,7 @@
         <v>18</v>
       </c>
       <c r="F62" t="str">
-        <f>IF(Dati_grezzi!C62&lt;=$O$2,"Basso",IF(C62&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C62&lt;=$J$2,"Basso",IF(C62&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G62">
@@ -3194,7 +3128,7 @@
         <v>18</v>
       </c>
       <c r="F63" t="str">
-        <f>IF(Dati_grezzi!C63&lt;=$O$2,"Basso",IF(C63&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C63&lt;=$J$2,"Basso",IF(C63&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G63">
@@ -3218,7 +3152,7 @@
         <v>18</v>
       </c>
       <c r="F64" t="str">
-        <f>IF(Dati_grezzi!C64&lt;=$O$2,"Basso",IF(C64&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C64&lt;=$J$2,"Basso",IF(C64&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G64">
@@ -3242,7 +3176,7 @@
         <v>18</v>
       </c>
       <c r="F65" t="str">
-        <f>IF(Dati_grezzi!C65&lt;=$O$2,"Basso",IF(C65&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C65&lt;=$J$2,"Basso",IF(C65&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G65">
@@ -3266,7 +3200,7 @@
         <v>18</v>
       </c>
       <c r="F66" t="str">
-        <f>IF(Dati_grezzi!C66&lt;=$O$2,"Basso",IF(C66&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C66&lt;=$J$2,"Basso",IF(C66&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G66">
@@ -3290,7 +3224,7 @@
         <v>18</v>
       </c>
       <c r="F67" t="str">
-        <f>IF(Dati_grezzi!C67&lt;=$O$2,"Basso",IF(C67&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C67&lt;=$J$2,"Basso",IF(C67&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G67">
@@ -3314,7 +3248,7 @@
         <v>18</v>
       </c>
       <c r="F68" t="str">
-        <f>IF(Dati_grezzi!C68&lt;=$O$2,"Basso",IF(C68&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C68&lt;=$J$2,"Basso",IF(C68&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G68">
@@ -3338,7 +3272,7 @@
         <v>18</v>
       </c>
       <c r="F69" t="str">
-        <f>IF(Dati_grezzi!C69&lt;=$O$2,"Basso",IF(C69&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C69&lt;=$J$2,"Basso",IF(C69&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G69">
@@ -3362,7 +3296,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="str">
-        <f>IF(Dati_grezzi!C70&lt;=$O$2,"Basso",IF(C70&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C70&lt;=$J$2,"Basso",IF(C70&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G70">
@@ -3386,7 +3320,7 @@
         <v>18</v>
       </c>
       <c r="F71" t="str">
-        <f>IF(Dati_grezzi!C71&lt;=$O$2,"Basso",IF(C71&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C71&lt;=$J$2,"Basso",IF(C71&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G71">
@@ -3410,7 +3344,7 @@
         <v>18</v>
       </c>
       <c r="F72" t="str">
-        <f>IF(Dati_grezzi!C72&lt;=$O$2,"Basso",IF(C72&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C72&lt;=$J$2,"Basso",IF(C72&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G72">
@@ -3434,7 +3368,7 @@
         <v>18</v>
       </c>
       <c r="F73" t="str">
-        <f>IF(Dati_grezzi!C73&lt;=$O$2,"Basso",IF(C73&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C73&lt;=$J$2,"Basso",IF(C73&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G73">
@@ -3458,7 +3392,7 @@
         <v>18</v>
       </c>
       <c r="F74" t="str">
-        <f>IF(Dati_grezzi!C74&lt;=$O$2,"Basso",IF(C74&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C74&lt;=$J$2,"Basso",IF(C74&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G74">
@@ -3482,7 +3416,7 @@
         <v>18</v>
       </c>
       <c r="F75" t="str">
-        <f>IF(Dati_grezzi!C75&lt;=$O$2,"Basso",IF(C75&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C75&lt;=$J$2,"Basso",IF(C75&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G75">
@@ -3506,7 +3440,7 @@
         <v>18</v>
       </c>
       <c r="F76" t="str">
-        <f>IF(Dati_grezzi!C76&lt;=$O$2,"Basso",IF(C76&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C76&lt;=$J$2,"Basso",IF(C76&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G76">
@@ -3530,7 +3464,7 @@
         <v>18</v>
       </c>
       <c r="F77" t="str">
-        <f>IF(Dati_grezzi!C77&lt;=$O$2,"Basso",IF(C77&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C77&lt;=$J$2,"Basso",IF(C77&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G77">
@@ -3554,7 +3488,7 @@
         <v>18</v>
       </c>
       <c r="F78" t="str">
-        <f>IF(Dati_grezzi!C78&lt;=$O$2,"Basso",IF(C78&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C78&lt;=$J$2,"Basso",IF(C78&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G78">
@@ -3578,7 +3512,7 @@
         <v>18</v>
       </c>
       <c r="F79" t="str">
-        <f>IF(Dati_grezzi!C79&lt;=$O$2,"Basso",IF(C79&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C79&lt;=$J$2,"Basso",IF(C79&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G79">
@@ -3602,7 +3536,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="str">
-        <f>IF(Dati_grezzi!C80&lt;=$O$2,"Basso",IF(C80&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C80&lt;=$J$2,"Basso",IF(C80&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G80">
@@ -3626,7 +3560,7 @@
         <v>18</v>
       </c>
       <c r="F81" t="str">
-        <f>IF(Dati_grezzi!C81&lt;=$O$2,"Basso",IF(C81&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C81&lt;=$J$2,"Basso",IF(C81&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G81">
@@ -3650,7 +3584,7 @@
         <v>18</v>
       </c>
       <c r="F82" t="str">
-        <f>IF(Dati_grezzi!C82&lt;=$O$2,"Basso",IF(C82&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C82&lt;=$J$2,"Basso",IF(C82&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G82">
@@ -3674,7 +3608,7 @@
         <v>18</v>
       </c>
       <c r="F83" t="str">
-        <f>IF(Dati_grezzi!C83&lt;=$O$2,"Basso",IF(C83&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C83&lt;=$J$2,"Basso",IF(C83&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G83">
@@ -3698,7 +3632,7 @@
         <v>18</v>
       </c>
       <c r="F84" t="str">
-        <f>IF(Dati_grezzi!C84&lt;=$O$2,"Basso",IF(C84&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C84&lt;=$J$2,"Basso",IF(C84&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G84">
@@ -3722,7 +3656,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="str">
-        <f>IF(Dati_grezzi!C85&lt;=$O$2,"Basso",IF(C85&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C85&lt;=$J$2,"Basso",IF(C85&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G85">
@@ -3746,7 +3680,7 @@
         <v>18</v>
       </c>
       <c r="F86" t="str">
-        <f>IF(Dati_grezzi!C86&lt;=$O$2,"Basso",IF(C86&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C86&lt;=$J$2,"Basso",IF(C86&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G86">
@@ -3770,7 +3704,7 @@
         <v>18</v>
       </c>
       <c r="F87" t="str">
-        <f>IF(Dati_grezzi!C87&lt;=$O$2,"Basso",IF(C87&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C87&lt;=$J$2,"Basso",IF(C87&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G87">
@@ -3794,7 +3728,7 @@
         <v>18</v>
       </c>
       <c r="F88" t="str">
-        <f>IF(Dati_grezzi!C88&lt;=$O$2,"Basso",IF(C88&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C88&lt;=$J$2,"Basso",IF(C88&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G88">
@@ -3818,7 +3752,7 @@
         <v>18</v>
       </c>
       <c r="F89" t="str">
-        <f>IF(Dati_grezzi!C89&lt;=$O$2,"Basso",IF(C89&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C89&lt;=$J$2,"Basso",IF(C89&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G89">
@@ -3842,7 +3776,7 @@
         <v>18</v>
       </c>
       <c r="F90" t="str">
-        <f>IF(Dati_grezzi!C90&lt;=$O$2,"Basso",IF(C90&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C90&lt;=$J$2,"Basso",IF(C90&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G90">
@@ -3866,7 +3800,7 @@
         <v>18</v>
       </c>
       <c r="F91" t="str">
-        <f>IF(Dati_grezzi!C91&lt;=$O$2,"Basso",IF(C91&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C91&lt;=$J$2,"Basso",IF(C91&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G91">
@@ -3890,7 +3824,7 @@
         <v>18</v>
       </c>
       <c r="F92" t="str">
-        <f>IF(Dati_grezzi!C92&lt;=$O$2,"Basso",IF(C92&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C92&lt;=$J$2,"Basso",IF(C92&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G92">
@@ -3914,7 +3848,7 @@
         <v>18</v>
       </c>
       <c r="F93" t="str">
-        <f>IF(Dati_grezzi!C93&lt;=$O$2,"Basso",IF(C93&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C93&lt;=$J$2,"Basso",IF(C93&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G93">
@@ -3938,7 +3872,7 @@
         <v>18</v>
       </c>
       <c r="F94" t="str">
-        <f>IF(Dati_grezzi!C94&lt;=$O$2,"Basso",IF(C94&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C94&lt;=$J$2,"Basso",IF(C94&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G94">
@@ -3962,7 +3896,7 @@
         <v>18</v>
       </c>
       <c r="F95" t="str">
-        <f>IF(Dati_grezzi!C95&lt;=$O$2,"Basso",IF(C95&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C95&lt;=$J$2,"Basso",IF(C95&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G95">
@@ -3986,7 +3920,7 @@
         <v>18</v>
       </c>
       <c r="F96" t="str">
-        <f>IF(Dati_grezzi!C96&lt;=$O$2,"Basso",IF(C96&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C96&lt;=$J$2,"Basso",IF(C96&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G96">
@@ -4010,7 +3944,7 @@
         <v>18</v>
       </c>
       <c r="F97" t="str">
-        <f>IF(Dati_grezzi!C97&lt;=$O$2,"Basso",IF(C97&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C97&lt;=$J$2,"Basso",IF(C97&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G97">
@@ -4034,7 +3968,7 @@
         <v>18</v>
       </c>
       <c r="F98" t="str">
-        <f>IF(Dati_grezzi!C98&lt;=$O$2,"Basso",IF(C98&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C98&lt;=$J$2,"Basso",IF(C98&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G98">
@@ -4058,7 +3992,7 @@
         <v>18</v>
       </c>
       <c r="F99" t="str">
-        <f>IF(Dati_grezzi!C99&lt;=$O$2,"Basso",IF(C99&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C99&lt;=$J$2,"Basso",IF(C99&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G99">
@@ -4082,7 +4016,7 @@
         <v>18</v>
       </c>
       <c r="F100" t="str">
-        <f>IF(Dati_grezzi!C100&lt;=$O$2,"Basso",IF(C100&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C100&lt;=$J$2,"Basso",IF(C100&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G100">
@@ -4106,7 +4040,7 @@
         <v>18</v>
       </c>
       <c r="F101" t="str">
-        <f>IF(Dati_grezzi!C101&lt;=$O$2,"Basso",IF(C101&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C101&lt;=$J$2,"Basso",IF(C101&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G101">
@@ -4130,7 +4064,7 @@
         <v>19</v>
       </c>
       <c r="F102" t="str">
-        <f>IF(Dati_grezzi!C102&lt;=$O$2,"Basso",IF(C102&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C102&lt;=$J$2,"Basso",IF(C102&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G102">
@@ -4154,7 +4088,7 @@
         <v>19</v>
       </c>
       <c r="F103" t="str">
-        <f>IF(Dati_grezzi!C103&lt;=$O$2,"Basso",IF(C103&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C103&lt;=$J$2,"Basso",IF(C103&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G103">
@@ -4178,7 +4112,7 @@
         <v>19</v>
       </c>
       <c r="F104" t="str">
-        <f>IF(Dati_grezzi!C104&lt;=$O$2,"Basso",IF(C104&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C104&lt;=$J$2,"Basso",IF(C104&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G104">
@@ -4202,7 +4136,7 @@
         <v>19</v>
       </c>
       <c r="F105" t="str">
-        <f>IF(Dati_grezzi!C105&lt;=$O$2,"Basso",IF(C105&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C105&lt;=$J$2,"Basso",IF(C105&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G105">
@@ -4226,7 +4160,7 @@
         <v>19</v>
       </c>
       <c r="F106" t="str">
-        <f>IF(Dati_grezzi!C106&lt;=$O$2,"Basso",IF(C106&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C106&lt;=$J$2,"Basso",IF(C106&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G106">
@@ -4250,7 +4184,7 @@
         <v>19</v>
       </c>
       <c r="F107" t="str">
-        <f>IF(Dati_grezzi!C107&lt;=$O$2,"Basso",IF(C107&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C107&lt;=$J$2,"Basso",IF(C107&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G107">
@@ -4274,7 +4208,7 @@
         <v>19</v>
       </c>
       <c r="F108" t="str">
-        <f>IF(Dati_grezzi!C108&lt;=$O$2,"Basso",IF(C108&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C108&lt;=$J$2,"Basso",IF(C108&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G108">
@@ -4298,7 +4232,7 @@
         <v>19</v>
       </c>
       <c r="F109" t="str">
-        <f>IF(Dati_grezzi!C109&lt;=$O$2,"Basso",IF(C109&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C109&lt;=$J$2,"Basso",IF(C109&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G109">
@@ -4322,7 +4256,7 @@
         <v>19</v>
       </c>
       <c r="F110" t="str">
-        <f>IF(Dati_grezzi!C110&lt;=$O$2,"Basso",IF(C110&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C110&lt;=$J$2,"Basso",IF(C110&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G110">
@@ -4346,7 +4280,7 @@
         <v>19</v>
       </c>
       <c r="F111" t="str">
-        <f>IF(Dati_grezzi!C111&lt;=$O$2,"Basso",IF(C111&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C111&lt;=$J$2,"Basso",IF(C111&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G111">
@@ -4370,7 +4304,7 @@
         <v>19</v>
       </c>
       <c r="F112" t="str">
-        <f>IF(Dati_grezzi!C112&lt;=$O$2,"Basso",IF(C112&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C112&lt;=$J$2,"Basso",IF(C112&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G112">
@@ -4394,7 +4328,7 @@
         <v>19</v>
       </c>
       <c r="F113" t="str">
-        <f>IF(Dati_grezzi!C113&lt;=$O$2,"Basso",IF(C113&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C113&lt;=$J$2,"Basso",IF(C113&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G113">
@@ -4418,7 +4352,7 @@
         <v>19</v>
       </c>
       <c r="F114" t="str">
-        <f>IF(Dati_grezzi!C114&lt;=$O$2,"Basso",IF(C114&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C114&lt;=$J$2,"Basso",IF(C114&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G114">
@@ -4442,7 +4376,7 @@
         <v>19</v>
       </c>
       <c r="F115" t="str">
-        <f>IF(Dati_grezzi!C115&lt;=$O$2,"Basso",IF(C115&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C115&lt;=$J$2,"Basso",IF(C115&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G115">
@@ -4466,7 +4400,7 @@
         <v>19</v>
       </c>
       <c r="F116" t="str">
-        <f>IF(Dati_grezzi!C116&lt;=$O$2,"Basso",IF(C116&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C116&lt;=$J$2,"Basso",IF(C116&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G116">
@@ -4490,7 +4424,7 @@
         <v>19</v>
       </c>
       <c r="F117" t="str">
-        <f>IF(Dati_grezzi!C117&lt;=$O$2,"Basso",IF(C117&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C117&lt;=$J$2,"Basso",IF(C117&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G117">
@@ -4514,7 +4448,7 @@
         <v>19</v>
       </c>
       <c r="F118" t="str">
-        <f>IF(Dati_grezzi!C118&lt;=$O$2,"Basso",IF(C118&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C118&lt;=$J$2,"Basso",IF(C118&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G118">
@@ -4538,7 +4472,7 @@
         <v>19</v>
       </c>
       <c r="F119" t="str">
-        <f>IF(Dati_grezzi!C119&lt;=$O$2,"Basso",IF(C119&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C119&lt;=$J$2,"Basso",IF(C119&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G119">
@@ -4562,7 +4496,7 @@
         <v>19</v>
       </c>
       <c r="F120" t="str">
-        <f>IF(Dati_grezzi!C120&lt;=$O$2,"Basso",IF(C120&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C120&lt;=$J$2,"Basso",IF(C120&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G120">
@@ -4586,7 +4520,7 @@
         <v>19</v>
       </c>
       <c r="F121" t="str">
-        <f>IF(Dati_grezzi!C121&lt;=$O$2,"Basso",IF(C121&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C121&lt;=$J$2,"Basso",IF(C121&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G121">
@@ -4610,7 +4544,7 @@
         <v>19</v>
       </c>
       <c r="F122" t="str">
-        <f>IF(Dati_grezzi!C122&lt;=$O$2,"Basso",IF(C122&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C122&lt;=$J$2,"Basso",IF(C122&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G122">
@@ -4634,7 +4568,7 @@
         <v>19</v>
       </c>
       <c r="F123" t="str">
-        <f>IF(Dati_grezzi!C123&lt;=$O$2,"Basso",IF(C123&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C123&lt;=$J$2,"Basso",IF(C123&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G123">
@@ -4658,7 +4592,7 @@
         <v>19</v>
       </c>
       <c r="F124" t="str">
-        <f>IF(Dati_grezzi!C124&lt;=$O$2,"Basso",IF(C124&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C124&lt;=$J$2,"Basso",IF(C124&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G124">
@@ -4682,7 +4616,7 @@
         <v>19</v>
       </c>
       <c r="F125" t="str">
-        <f>IF(Dati_grezzi!C125&lt;=$O$2,"Basso",IF(C125&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C125&lt;=$J$2,"Basso",IF(C125&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G125">
@@ -4706,7 +4640,7 @@
         <v>19</v>
       </c>
       <c r="F126" t="str">
-        <f>IF(Dati_grezzi!C126&lt;=$O$2,"Basso",IF(C126&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C126&lt;=$J$2,"Basso",IF(C126&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G126">
@@ -4730,7 +4664,7 @@
         <v>19</v>
       </c>
       <c r="F127" t="str">
-        <f>IF(Dati_grezzi!C127&lt;=$O$2,"Basso",IF(C127&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C127&lt;=$J$2,"Basso",IF(C127&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G127">
@@ -4754,7 +4688,7 @@
         <v>19</v>
       </c>
       <c r="F128" t="str">
-        <f>IF(Dati_grezzi!C128&lt;=$O$2,"Basso",IF(C128&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C128&lt;=$J$2,"Basso",IF(C128&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G128">
@@ -4778,7 +4712,7 @@
         <v>19</v>
       </c>
       <c r="F129" t="str">
-        <f>IF(Dati_grezzi!C129&lt;=$O$2,"Basso",IF(C129&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C129&lt;=$J$2,"Basso",IF(C129&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G129">
@@ -4802,7 +4736,7 @@
         <v>19</v>
       </c>
       <c r="F130" t="str">
-        <f>IF(Dati_grezzi!C130&lt;=$O$2,"Basso",IF(C130&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C130&lt;=$J$2,"Basso",IF(C130&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G130">
@@ -4826,7 +4760,7 @@
         <v>19</v>
       </c>
       <c r="F131" t="str">
-        <f>IF(Dati_grezzi!C131&lt;=$O$2,"Basso",IF(C131&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C131&lt;=$J$2,"Basso",IF(C131&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G131">
@@ -4850,7 +4784,7 @@
         <v>19</v>
       </c>
       <c r="F132" t="str">
-        <f>IF(Dati_grezzi!C132&lt;=$O$2,"Basso",IF(C132&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C132&lt;=$J$2,"Basso",IF(C132&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G132">
@@ -4874,7 +4808,7 @@
         <v>19</v>
       </c>
       <c r="F133" t="str">
-        <f>IF(Dati_grezzi!C133&lt;=$O$2,"Basso",IF(C133&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C133&lt;=$J$2,"Basso",IF(C133&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G133">
@@ -4898,7 +4832,7 @@
         <v>19</v>
       </c>
       <c r="F134" t="str">
-        <f>IF(Dati_grezzi!C134&lt;=$O$2,"Basso",IF(C134&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C134&lt;=$J$2,"Basso",IF(C134&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G134">
@@ -4922,7 +4856,7 @@
         <v>19</v>
       </c>
       <c r="F135" t="str">
-        <f>IF(Dati_grezzi!C135&lt;=$O$2,"Basso",IF(C135&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C135&lt;=$J$2,"Basso",IF(C135&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G135">
@@ -4946,7 +4880,7 @@
         <v>19</v>
       </c>
       <c r="F136" t="str">
-        <f>IF(Dati_grezzi!C136&lt;=$O$2,"Basso",IF(C136&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C136&lt;=$J$2,"Basso",IF(C136&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G136">
@@ -4970,7 +4904,7 @@
         <v>19</v>
       </c>
       <c r="F137" t="str">
-        <f>IF(Dati_grezzi!C137&lt;=$O$2,"Basso",IF(C137&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C137&lt;=$J$2,"Basso",IF(C137&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G137">
@@ -4994,7 +4928,7 @@
         <v>19</v>
       </c>
       <c r="F138" t="str">
-        <f>IF(Dati_grezzi!C138&lt;=$O$2,"Basso",IF(C138&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C138&lt;=$J$2,"Basso",IF(C138&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G138">
@@ -5018,7 +4952,7 @@
         <v>19</v>
       </c>
       <c r="F139" t="str">
-        <f>IF(Dati_grezzi!C139&lt;=$O$2,"Basso",IF(C139&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C139&lt;=$J$2,"Basso",IF(C139&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G139">
@@ -5042,7 +4976,7 @@
         <v>19</v>
       </c>
       <c r="F140" t="str">
-        <f>IF(Dati_grezzi!C140&lt;=$O$2,"Basso",IF(C140&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C140&lt;=$J$2,"Basso",IF(C140&lt;=$J$3,"Medio","Alto"))</f>
         <v>Medio</v>
       </c>
       <c r="G140">
@@ -5066,7 +5000,7 @@
         <v>19</v>
       </c>
       <c r="F141" t="str">
-        <f>IF(Dati_grezzi!C141&lt;=$O$2,"Basso",IF(C141&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C141&lt;=$J$2,"Basso",IF(C141&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G141">
@@ -5090,7 +5024,7 @@
         <v>19</v>
       </c>
       <c r="F142" t="str">
-        <f>IF(Dati_grezzi!C142&lt;=$O$2,"Basso",IF(C142&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C142&lt;=$J$2,"Basso",IF(C142&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G142">
@@ -5114,7 +5048,7 @@
         <v>19</v>
       </c>
       <c r="F143" t="str">
-        <f>IF(Dati_grezzi!C143&lt;=$O$2,"Basso",IF(C143&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C143&lt;=$J$2,"Basso",IF(C143&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G143">
@@ -5138,7 +5072,7 @@
         <v>19</v>
       </c>
       <c r="F144" t="str">
-        <f>IF(Dati_grezzi!C144&lt;=$O$2,"Basso",IF(C144&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C144&lt;=$J$2,"Basso",IF(C144&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G144">
@@ -5162,7 +5096,7 @@
         <v>19</v>
       </c>
       <c r="F145" t="str">
-        <f>IF(Dati_grezzi!C145&lt;=$O$2,"Basso",IF(C145&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C145&lt;=$J$2,"Basso",IF(C145&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G145">
@@ -5186,7 +5120,7 @@
         <v>19</v>
       </c>
       <c r="F146" t="str">
-        <f>IF(Dati_grezzi!C146&lt;=$O$2,"Basso",IF(C146&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C146&lt;=$J$2,"Basso",IF(C146&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G146">
@@ -5210,7 +5144,7 @@
         <v>19</v>
       </c>
       <c r="F147" t="str">
-        <f>IF(Dati_grezzi!C147&lt;=$O$2,"Basso",IF(C147&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C147&lt;=$J$2,"Basso",IF(C147&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G147">
@@ -5234,7 +5168,7 @@
         <v>19</v>
       </c>
       <c r="F148" t="str">
-        <f>IF(Dati_grezzi!C148&lt;=$O$2,"Basso",IF(C148&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C148&lt;=$J$2,"Basso",IF(C148&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G148">
@@ -5258,7 +5192,7 @@
         <v>19</v>
       </c>
       <c r="F149" t="str">
-        <f>IF(Dati_grezzi!C149&lt;=$O$2,"Basso",IF(C149&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C149&lt;=$J$2,"Basso",IF(C149&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G149">
@@ -5282,7 +5216,7 @@
         <v>19</v>
       </c>
       <c r="F150" t="str">
-        <f>IF(Dati_grezzi!C150&lt;=$O$2,"Basso",IF(C150&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C150&lt;=$J$2,"Basso",IF(C150&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G150">
@@ -5306,7 +5240,7 @@
         <v>19</v>
       </c>
       <c r="F151" t="str">
-        <f>IF(Dati_grezzi!C151&lt;=$O$2,"Basso",IF(C151&lt;=$O$3,"Medio","Alto"))</f>
+        <f>IF(Dati_grezzi!C151&lt;=$J$2,"Basso",IF(C151&lt;=$J$3,"Medio","Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="G151">
@@ -10648,556 +10582,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E32CF21-0BFF-4609-807B-E20BDED60E91}">
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>19</v>
-      </c>
-      <c r="B48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>19</v>
-      </c>
-      <c r="B50" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96728C41-8E02-447C-B88F-59C6DBB20D94}">
   <dimension ref="A2:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11243,12 +10627,10 @@
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13">
+      <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13">
+      <c r="E5">
         <v>50</v>
       </c>
     </row>
@@ -11256,14 +10638,13 @@
       <c r="A6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13">
+      <c r="D6">
         <v>48</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6">
         <v>50</v>
       </c>
     </row>
@@ -11271,14 +10652,13 @@
       <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7">
         <v>44</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13">
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7">
         <v>50</v>
       </c>
     </row>
@@ -11286,16 +10666,16 @@
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8">
         <v>46</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8">
         <v>50</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8">
         <v>54</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8">
         <v>150</v>
       </c>
     </row>
@@ -11383,14 +10763,61 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="674b27b8-e1cd-4723-9694-0b904cc35f92">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11572,20 +10999,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="674b27b8-e1cd-4723-9694-0b904cc35f92">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9910A44-9D4B-4AE0-8F32-468CD0F680ED}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAACB6A-3780-4878-A77A-6EE417743D34}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="674b27b8-e1cd-4723-9694-0b904cc35f92"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11609,9 +11035,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAACB6A-3780-4878-A77A-6EE417743D34}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9910A44-9D4B-4AE0-8F32-468CD0F680ED}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="674b27b8-e1cd-4723-9694-0b904cc35f92"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>